--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260817_201404.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260817_201404.xlsx
@@ -6480,7 +6480,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260817_201404.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260817_201404.xlsx
@@ -6480,7 +6480,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7072,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
